--- a/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day1.xlsx
+++ b/Download/Assets/Resources/4. Data/1. VisualNovel/Dialogs/Dialogs_Day1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dadi2\OneDrive\문서\카카오톡 받은 파일\사운드 다이얼로그\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gksk7\Desktop\Download\Download\Assets\Resources\4. Data\1. VisualNovel\Dialogs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064487D7-3620-4115-BFE4-1E2C101D68B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97401F45-D53F-4976-8104-A4E10992099C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-114" yWindow="-114" windowWidth="27602" windowHeight="15027" tabRatio="638" firstSheet="17" activeTab="23" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="638" firstSheet="16" activeTab="23" xr2:uid="{49FB8DDA-CC9A-4F10-83A2-6EE5D727B386}"/>
   </bookViews>
   <sheets>
     <sheet name="S00_1_SchoolGo" sheetId="1" r:id="rId1"/>
@@ -57,7 +57,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4542" uniqueCount="1181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4557" uniqueCount="1184">
   <si>
     <t>dialogType</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52800,17 +52800,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>{KI03}</t>
-  </si>
-  <si>
-    <t>{KI03}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">{KI01} </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>{KI01}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -52859,6 +52848,30 @@
   </si>
   <si>
     <t>네가 뭘 해도 싫지 않아.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF13</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF08</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF09</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF17</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF07</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>EF10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -56726,9 +56739,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 테마">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -56766,7 +56779,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -56872,7 +56885,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -57014,7 +57027,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -57023,7 +57036,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B15E6C3-7F7C-4EB7-8D85-AD41865E955E}">
   <dimension ref="A1:S85"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.375" customWidth="1"/>
     <col min="2" max="2" width="9.25" customWidth="1"/>
@@ -57074,10 +57087,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -57351,7 +57364,7 @@
         <v>190</v>
       </c>
       <c r="J14" s="77" t="s">
-        <v>1170</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="15" spans="1:18">
@@ -58785,7 +58798,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE5C07FC-F76F-49F3-A83C-B514D5031AC0}">
   <dimension ref="A1:S16"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="19.75" customWidth="1"/>
     <col min="6" max="6" width="55.875" customWidth="1"/>
@@ -58821,10 +58834,10 @@
         <v>2</v>
       </c>
       <c r="I1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="J1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -58851,7 +58864,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="29.95">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>1</v>
       </c>
@@ -58931,7 +58944,7 @@
         <v>1073</v>
       </c>
       <c r="I5" s="77" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -59209,7 +59222,7 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8214A8B-6C9C-48ED-B88F-8190AC2B2136}">
   <dimension ref="A1:S33"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="19.75" customWidth="1"/>
     <col min="6" max="6" width="60.125" customWidth="1"/>
@@ -59246,10 +59259,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -59376,7 +59389,7 @@
         <v>1074</v>
       </c>
       <c r="J6" s="77" t="s">
-        <v>1176</v>
+        <v>1173</v>
       </c>
       <c r="K6">
         <v>2</v>
@@ -59959,7 +59972,7 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5035B1B-2E95-4088-8BF3-E4E5D26C1690}">
   <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="6" width="59.875" customWidth="1"/>
@@ -59996,10 +60009,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -60937,7 +60950,7 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{690429A1-5C87-4903-88E1-F8CE1CB0AD47}">
   <dimension ref="A1:S37"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="46.25" customWidth="1"/>
@@ -60974,10 +60987,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -61027,7 +61040,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="29.95">
+    <row r="3" spans="1:18" ht="27">
       <c r="A3">
         <v>1</v>
       </c>
@@ -61126,8 +61139,8 @@
       <c r="H7" t="s">
         <v>1070</v>
       </c>
-      <c r="J7" s="77">
-        <v>9</v>
+      <c r="J7" s="77" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="8" spans="1:18">
@@ -61170,7 +61183,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="29.95">
+    <row r="10" spans="1:18" ht="27">
       <c r="A10">
         <v>1</v>
       </c>
@@ -61330,7 +61343,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="29.95">
+    <row r="18" spans="1:10" ht="27">
       <c r="A18">
         <v>1</v>
       </c>
@@ -61350,7 +61363,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="29.95">
+    <row r="19" spans="1:10">
       <c r="A19">
         <v>1</v>
       </c>
@@ -61467,7 +61480,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="29.95">
+    <row r="25" spans="1:10" ht="27">
       <c r="A25">
         <v>1</v>
       </c>
@@ -61518,7 +61531,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="29.95">
+    <row r="28" spans="1:10" ht="27">
       <c r="A28">
         <v>1</v>
       </c>
@@ -61552,7 +61565,7 @@
         <v>1077</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="29.95">
+    <row r="30" spans="1:10" ht="27">
       <c r="A30">
         <v>1</v>
       </c>
@@ -61588,8 +61601,8 @@
       <c r="G31" t="s">
         <v>1077</v>
       </c>
-      <c r="J31" s="77">
-        <v>17</v>
+      <c r="J31" s="77" t="s">
+        <v>1181</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -61774,7 +61787,7 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B37A9212-2216-473D-A618-DED2D90469AB}">
   <dimension ref="A1:S71"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.625" customWidth="1"/>
     <col min="6" max="6" width="80.25" customWidth="1"/>
@@ -61816,10 +61829,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -61955,8 +61968,8 @@
       <c r="G8" t="s">
         <v>1066</v>
       </c>
-      <c r="J8" s="77">
-        <v>13</v>
+      <c r="J8" s="77" t="s">
+        <v>1178</v>
       </c>
     </row>
     <row r="9" spans="1:18">
@@ -62016,7 +62029,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="77" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="12" spans="1:18">
@@ -62359,7 +62372,7 @@
         <v>1079</v>
       </c>
       <c r="J28" s="77" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -62802,7 +62815,7 @@
         <v>1080</v>
       </c>
       <c r="J50" s="77" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="51" spans="1:10">
@@ -63248,7 +63261,7 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A0C0A81-5F7E-4B69-AE02-1CF499459232}">
   <dimension ref="A1:S20"/>
-  <sheetFormatPr defaultRowHeight="15.7" outlineLevelCol="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1"/>
   <cols>
     <col min="5" max="5" width="15.5" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -63287,10 +63300,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -63437,7 +63450,7 @@
         <v>1082</v>
       </c>
       <c r="J7" s="77" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="K7">
         <v>-2</v>
@@ -63758,7 +63771,7 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F349A6D-78FA-41E7-95C4-55356F8EDA95}">
   <dimension ref="A1:S50"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="6.75" customWidth="1"/>
     <col min="5" max="5" width="15.625" customWidth="1"/>
@@ -63798,10 +63811,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -64511,7 +64524,7 @@
         <v>1079</v>
       </c>
       <c r="J35" s="77" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -64848,7 +64861,7 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A88044D9-BAC4-4E6C-8C82-5F452811949D}">
   <dimension ref="A1:S108"/>
-  <sheetFormatPr defaultRowHeight="15.7" outlineLevelCol="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1"/>
   <cols>
     <col min="5" max="5" width="16.375" customWidth="1"/>
     <col min="6" max="6" width="70.125" customWidth="1"/>
@@ -64885,10 +64898,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -66867,7 +66880,7 @@
         <v>1080</v>
       </c>
       <c r="J98" s="77" t="s">
-        <v>1177</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="99" spans="1:10">
@@ -67104,7 +67117,7 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81ABA476-7B17-4809-8C4F-2F9B8D5E9BCC}">
   <dimension ref="A1:S52"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="6.75" customWidth="1"/>
     <col min="5" max="5" width="15.875" customWidth="1"/>
@@ -67142,10 +67155,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -67334,8 +67347,8 @@
       <c r="H9" t="s">
         <v>1079</v>
       </c>
-      <c r="J9" s="77">
-        <v>9</v>
+      <c r="J9" s="77" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="10" spans="1:18">
@@ -67358,7 +67371,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="24.25">
+    <row r="11" spans="1:18" ht="24">
       <c r="A11">
         <v>1</v>
       </c>
@@ -67418,7 +67431,7 @@
         <v>1083</v>
       </c>
       <c r="J13" s="77" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="14" spans="1:18">
@@ -67791,7 +67804,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="34" spans="1:10" ht="24.25">
+    <row r="34" spans="1:10" ht="24">
       <c r="A34">
         <v>1</v>
       </c>
@@ -67944,7 +67957,7 @@
         <v>1086</v>
       </c>
       <c r="J42" s="77" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="43" spans="1:10">
@@ -67980,8 +67993,8 @@
       <c r="G44" t="s">
         <v>1086</v>
       </c>
-      <c r="J44" s="77">
-        <v>17</v>
+      <c r="J44" s="77" t="s">
+        <v>1181</v>
       </c>
     </row>
     <row r="45" spans="1:10">
@@ -68018,7 +68031,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="24.25">
+    <row r="47" spans="1:10" ht="24">
       <c r="A47">
         <v>1</v>
       </c>
@@ -68183,7 +68196,7 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7773A5F6-BD94-47B5-855B-F05BA7AFF7BE}">
   <dimension ref="A1:S103"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="17" customWidth="1"/>
     <col min="6" max="6" width="73.125" customWidth="1"/>
@@ -68225,10 +68238,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -68483,8 +68496,8 @@
       <c r="G15" t="s">
         <v>1067</v>
       </c>
-      <c r="J15" s="77">
-        <v>7</v>
+      <c r="J15" s="77" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -68588,8 +68601,8 @@
       <c r="G21" t="s">
         <v>1067</v>
       </c>
-      <c r="J21" s="77">
-        <v>7</v>
+      <c r="J21" s="77" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -68676,8 +68689,8 @@
       <c r="G26" t="s">
         <v>1067</v>
       </c>
-      <c r="J26" s="77">
-        <v>10</v>
+      <c r="J26" s="77" t="s">
+        <v>1183</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -68854,7 +68867,7 @@
         <v>1087</v>
       </c>
       <c r="J35" s="77" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -69196,8 +69209,8 @@
       <c r="H52" t="s">
         <v>1088</v>
       </c>
-      <c r="J52" s="77">
-        <v>7</v>
+      <c r="J52" s="77" t="s">
+        <v>1182</v>
       </c>
     </row>
     <row r="53" spans="1:10">
@@ -69685,7 +69698,7 @@
         <v>1089</v>
       </c>
       <c r="J80" s="77" t="s">
-        <v>1178</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -70011,7 +70024,7 @@
         <v>1089</v>
       </c>
       <c r="J99" s="77" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="100" spans="1:15">
@@ -70174,7 +70187,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA2492B5-5286-4C51-A0EE-617DAAF7402C}">
   <dimension ref="A1:S42"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.375" customWidth="1"/>
     <col min="3" max="3" width="9.875" customWidth="1"/>
@@ -70221,10 +70234,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -70259,7 +70272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:18" ht="26.05" customHeight="1">
+    <row r="3" spans="1:18" ht="26.1" customHeight="1">
       <c r="A3">
         <v>1</v>
       </c>
@@ -70276,7 +70289,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="31.2" customHeight="1">
+    <row r="4" spans="1:18" ht="31.15" customHeight="1">
       <c r="A4">
         <v>1</v>
       </c>
@@ -70293,7 +70306,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="5" spans="1:18" ht="26.05" customHeight="1">
+    <row r="5" spans="1:18" ht="26.1" customHeight="1">
       <c r="A5">
         <v>1</v>
       </c>
@@ -70344,7 +70357,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="28.2" customHeight="1">
+    <row r="8" spans="1:18" ht="28.15" customHeight="1">
       <c r="A8">
         <v>1</v>
       </c>
@@ -70361,7 +70374,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="9" spans="1:18" ht="29.95" customHeight="1">
+    <row r="9" spans="1:18" ht="30" customHeight="1">
       <c r="A9">
         <v>1</v>
       </c>
@@ -70486,7 +70499,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="77" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="16" spans="1:18">
@@ -70888,8 +70901,8 @@
       <c r="H35" t="s">
         <v>196</v>
       </c>
-      <c r="J35" s="77">
-        <v>13</v>
+      <c r="J35" s="77" t="s">
+        <v>1178</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -71036,7 +71049,7 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2DDD60E3-191C-47F5-BDA8-2D655F79AB62}">
   <dimension ref="A1:S30"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.375" customWidth="1"/>
     <col min="6" max="6" width="68.625" customWidth="1"/>
@@ -71075,10 +71088,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -71288,7 +71301,7 @@
         <v>1087</v>
       </c>
       <c r="J10" s="77" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="11" spans="1:18">
@@ -71666,7 +71679,7 @@
         <v>18</v>
       </c>
       <c r="F29" s="74" t="s">
-        <v>1180</v>
+        <v>1177</v>
       </c>
       <c r="G29" t="s">
         <v>1067</v>
@@ -71750,7 +71763,7 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0A57258B-2DAB-4C21-BB34-62EF444C66FC}">
   <dimension ref="A1:S41"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.25" customWidth="1"/>
     <col min="6" max="6" width="62.75" customWidth="1"/>
@@ -71787,10 +71800,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -72457,7 +72470,7 @@
         <v>1067</v>
       </c>
       <c r="H33" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="34" spans="1:10">
@@ -72477,7 +72490,7 @@
         <v>1067</v>
       </c>
       <c r="H34" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="J34" s="77" t="s">
         <v>1089</v>
@@ -72500,7 +72513,7 @@
         <v>1067</v>
       </c>
       <c r="H35" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="36" spans="1:10">
@@ -72520,7 +72533,7 @@
         <v>1067</v>
       </c>
       <c r="H36" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="37" spans="1:10">
@@ -72540,7 +72553,7 @@
         <v>1067</v>
       </c>
       <c r="H37" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -72657,7 +72670,7 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00B55310-7DFB-4209-9270-E7C77F50F6F4}">
   <dimension ref="A1:S37"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="4" max="4" width="6.75" customWidth="1"/>
     <col min="5" max="5" width="18.75" customWidth="1"/>
@@ -72697,10 +72710,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -73270,7 +73283,7 @@
         <v>1067</v>
       </c>
       <c r="H28" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -73290,7 +73303,7 @@
         <v>1067</v>
       </c>
       <c r="H29" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
       <c r="J29" s="77" t="s">
         <v>1089</v>
@@ -73313,7 +73326,7 @@
         <v>1067</v>
       </c>
       <c r="H30" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -73353,7 +73366,7 @@
         <v>1067</v>
       </c>
       <c r="H32" t="s">
-        <v>1168</v>
+        <v>1165</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -73490,7 +73503,7 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FC7C0B1-4AC5-4D8F-862A-CBFE759818AD}">
   <dimension ref="A1:R37"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.125" customWidth="1"/>
     <col min="6" max="6" width="60.75" customWidth="1"/>
@@ -73525,10 +73538,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -73598,7 +73611,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="24.25">
+    <row r="4" spans="1:18" ht="24">
       <c r="A4">
         <v>1</v>
       </c>
@@ -73850,8 +73863,8 @@
       <c r="G17" t="s">
         <v>1096</v>
       </c>
-      <c r="J17">
-        <v>17</v>
+      <c r="J17" t="s">
+        <v>1181</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -74112,7 +74125,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="33" spans="1:9" ht="24.25">
+    <row r="33" spans="1:9" ht="24">
       <c r="A33">
         <v>1</v>
       </c>
@@ -74298,7 +74311,7 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C39CDF1-357E-420D-87FA-2B790238D216}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="18.75" customWidth="1"/>
     <col min="6" max="6" width="55.25" customWidth="1"/>
@@ -74335,10 +74348,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -74730,7 +74743,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="24.25">
+    <row r="24" spans="1:18" ht="24">
       <c r="A24">
         <v>1</v>
       </c>
@@ -74866,7 +74879,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{609C6A72-ACFC-487E-9E99-9EC3E4487846}">
   <dimension ref="A1:S63"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="3" max="3" width="11" customWidth="1"/>
@@ -74912,10 +74925,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -75154,7 +75167,7 @@
         <v>200</v>
       </c>
       <c r="J12" s="77" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="S12" s="77"/>
     </row>
@@ -75178,7 +75191,7 @@
         <v>201</v>
       </c>
       <c r="J13" s="77" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="S13" s="77"/>
     </row>
@@ -75321,8 +75334,8 @@
       <c r="H20" t="s">
         <v>202</v>
       </c>
-      <c r="J20" s="77">
-        <v>8</v>
+      <c r="J20" s="77" t="s">
+        <v>1179</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -75825,7 +75838,7 @@
         <v>207</v>
       </c>
       <c r="J45" s="77" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="S45" s="77"/>
     </row>
@@ -76109,7 +76122,7 @@
         <v>207</v>
       </c>
       <c r="J59" s="77" t="s">
-        <v>191</v>
+        <v>1072</v>
       </c>
       <c r="S59" s="77"/>
     </row>
@@ -76235,7 +76248,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271B8C6D-E66C-49CA-85A0-5A214B1CC69B}">
   <dimension ref="A1:S63"/>
-  <sheetFormatPr defaultRowHeight="15.7" outlineLevelCol="1"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="3" max="3" width="10.125" customWidth="1"/>
@@ -76281,10 +76294,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -76359,7 +76372,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="29.95">
+    <row r="4" spans="1:19">
       <c r="A4">
         <v>1</v>
       </c>
@@ -76559,7 +76572,7 @@
         <v>201</v>
       </c>
       <c r="J13" s="77" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="S13" s="77"/>
     </row>
@@ -77019,7 +77032,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48928998-9BC0-4C0B-A755-254B564BF033}">
   <dimension ref="A1:S63"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="3" max="3" width="9.875" customWidth="1"/>
@@ -77065,10 +77078,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -77115,7 +77128,7 @@
         <v>201</v>
       </c>
       <c r="J2" s="77" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
       <c r="K2">
         <v>1</v>
@@ -77181,7 +77194,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="6" spans="1:18" ht="29.95">
+    <row r="6" spans="1:18">
       <c r="A6">
         <v>1</v>
       </c>
@@ -77461,7 +77474,7 @@
         <v>200</v>
       </c>
       <c r="J19" s="77" t="s">
-        <v>1173</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -77644,7 +77657,7 @@
         <v>201</v>
       </c>
       <c r="J28" s="77" t="s">
-        <v>1171</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -78044,7 +78057,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6397B58-A896-46D5-8199-88C0AF89D37B}">
   <dimension ref="A1:S95"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.625" customWidth="1"/>
     <col min="3" max="3" width="10.25" customWidth="1"/>
@@ -78090,10 +78103,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -78503,10 +78516,10 @@
         <v>1164</v>
       </c>
       <c r="J20" s="77" t="s">
-        <v>1174</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" ht="27.1">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="26.25">
       <c r="A21">
         <v>1</v>
       </c>
@@ -78566,7 +78579,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="164.7">
+    <row r="24" spans="1:10" ht="152.25">
       <c r="A24">
         <v>1</v>
       </c>
@@ -78629,7 +78642,7 @@
         <v>1160</v>
       </c>
       <c r="J26" s="77" t="s">
-        <v>1167</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -78792,7 +78805,7 @@
         <v>312</v>
       </c>
       <c r="J34" s="77" t="s">
-        <v>196</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="35" spans="1:10">
@@ -79015,7 +79028,7 @@
         <v>202</v>
       </c>
       <c r="J45" s="77" t="s">
-        <v>1166</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="46" spans="1:10">
@@ -79273,7 +79286,7 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1FD9133-E9CE-442F-8E83-F0C8F07C3659}">
   <dimension ref="A1:S51"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="17.375" customWidth="1"/>
     <col min="6" max="6" width="81.625" customWidth="1"/>
@@ -79310,10 +79323,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -79399,8 +79412,8 @@
       <c r="H4" t="s">
         <v>200</v>
       </c>
-      <c r="J4" s="77">
-        <v>8</v>
+      <c r="J4" s="77" t="s">
+        <v>1179</v>
       </c>
     </row>
     <row r="5" spans="1:18">
@@ -79706,7 +79719,7 @@
         <v>381</v>
       </c>
       <c r="J19" s="77" t="s">
-        <v>1172</v>
+        <v>1169</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -79805,8 +79818,8 @@
       <c r="G24" t="s">
         <v>382</v>
       </c>
-      <c r="J24" s="77">
-        <v>9</v>
+      <c r="J24" s="77" t="s">
+        <v>1180</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -80333,7 +80346,7 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6E221C43-E802-4C8D-BB36-87BBB4F43803}">
   <dimension ref="A1:R26"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="13.75" customWidth="1"/>
     <col min="6" max="6" width="78.625" customWidth="1"/>
@@ -80371,10 +80384,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -80868,7 +80881,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5684E33D-FE1A-4734-9579-F1C91C61DC51}">
   <dimension ref="A1:S57"/>
-  <sheetFormatPr defaultRowHeight="15.7"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="5" max="5" width="15.125" customWidth="1"/>
     <col min="6" max="6" width="76.25" customWidth="1"/>
@@ -80910,10 +80923,10 @@
         <v>2</v>
       </c>
       <c r="I1" t="s">
-        <v>1169</v>
+        <v>1166</v>
       </c>
       <c r="J1" s="77" t="s">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="K1" t="s">
         <v>3</v>
@@ -80998,8 +81011,8 @@
       <c r="G5" t="s">
         <v>1065</v>
       </c>
-      <c r="J5" s="77">
-        <v>13</v>
+      <c r="J5" s="77" t="s">
+        <v>1178</v>
       </c>
     </row>
     <row r="6" spans="1:18">
@@ -81195,7 +81208,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="77" t="s">
-        <v>1175</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -81598,7 +81611,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="29.95">
+    <row r="37" spans="1:10">
       <c r="A37">
         <v>1</v>
       </c>
